--- a/output/laminas_comunales/comunal_o_ocup_a_2023_nuble.xlsx
+++ b/output/laminas_comunales/comunal_o_ocup_a_2023_nuble.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C148"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -375,256 +375,256 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>16103</t>
+          <t>16101</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Chillán Viejo</t>
+          <t>Chillán</t>
         </is>
       </c>
       <c r="C2">
-        <v>38.7302282243851</v>
+        <v>57.1826596499086</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>16303</t>
+          <t>16103</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ñiquén</t>
+          <t>Chillán Viejo</t>
         </is>
       </c>
       <c r="C3">
-        <v>36.2559347845561</v>
+        <v>56.8546306220476</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>16101</t>
+          <t>16203</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Chillán</t>
+          <t>Coelemu</t>
         </is>
       </c>
       <c r="C4">
-        <v>36.0462938913084</v>
+        <v>55.3005314275243</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>16206</t>
+          <t>16109</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ranquil</t>
+          <t>Yungay</t>
         </is>
       </c>
       <c r="C5">
-        <v>34.1796341796342</v>
+        <v>54.8488054306621</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>16203</t>
+          <t>16206</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Coelemu</t>
+          <t>Ranquil</t>
         </is>
       </c>
       <c r="C6">
-        <v>33.3565459610028</v>
+        <v>54.5501820072803</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>16109</t>
+          <t>16207</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Yungay</t>
+          <t>Treguaco</t>
         </is>
       </c>
       <c r="C7">
-        <v>31.8803684156059</v>
+        <v>53.6612021857923</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>16102</t>
+          <t>16201</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bulnes</t>
+          <t>Quirihue</t>
         </is>
       </c>
       <c r="C8">
-        <v>31.7572542052784</v>
+        <v>53.3255993812838</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>16305</t>
+          <t>16102</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>San Nicolás</t>
+          <t>Bulnes</t>
         </is>
       </c>
       <c r="C9">
-        <v>31.4467458478177</v>
+        <v>51.3902881321781</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>16201</t>
+          <t>16105</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Quirihue</t>
+          <t>Pemuco</t>
         </is>
       </c>
       <c r="C10">
-        <v>30.840469099032</v>
+        <v>50.2698024842191</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>16302</t>
+          <t>16301</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Coihueco</t>
+          <t>San Carlos</t>
         </is>
       </c>
       <c r="C11">
-        <v>30.478195164076</v>
+        <v>50.0696496411988</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>16105</t>
+          <t>16305</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Pemuco</t>
+          <t>San Nicolás</t>
         </is>
       </c>
       <c r="C12">
-        <v>30.0612020354834</v>
+        <v>49.9290259422418</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>16301</t>
+          <t>16303</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>San Carlos</t>
+          <t>Ñiquén</t>
         </is>
       </c>
       <c r="C13">
-        <v>29.9374137895539</v>
+        <v>48.5775862068966</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>16207</t>
+          <t>16302</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Treguaco</t>
+          <t>Coihueco</t>
         </is>
       </c>
       <c r="C14">
-        <v>29.8663820366856</v>
+        <v>48.3906947100064</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>16304</t>
+          <t>16205</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>San Fabián</t>
+          <t>Portezuelo</t>
         </is>
       </c>
       <c r="C15">
-        <v>27.673434856176</v>
+        <v>48.2635658914729</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>16106</t>
+          <t>16103</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Pinto</t>
+          <t>Chillán Viejo</t>
         </is>
       </c>
       <c r="C16">
-        <v>26.1446551116174</v>
+        <v>48.0977099888917</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>16205</t>
+          <t>16101</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Portezuelo</t>
+          <t>Chillán</t>
         </is>
       </c>
       <c r="C17">
-        <v>25.8428627760252</v>
+        <v>47.957169025524</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>16104</t>
+          <t>16203</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>El Carmen</t>
+          <t>Coelemu</t>
         </is>
       </c>
       <c r="C18">
-        <v>25.7326085715916</v>
+        <v>45.8077299848606</v>
       </c>
     </row>
     <row r="19">
@@ -639,52 +639,1942 @@
         </is>
       </c>
       <c r="C19">
-        <v>25.5583909559873</v>
+        <v>45.7728620474407</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>16108</t>
+          <t>16304</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>San Ignacio</t>
+          <t>San Fabián</t>
         </is>
       </c>
       <c r="C20">
-        <v>24.9593179567002</v>
+        <v>45.7416142557652</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>16204</t>
+          <t>16104</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ninhue</t>
+          <t>El Carmen</t>
         </is>
       </c>
       <c r="C21">
-        <v>23.1709333862539</v>
+        <v>45.3418482344102</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>44.9864073609368</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>44.7301587301587</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>44.6749791089414</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>44.3007031421666</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>16303</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Ñiquén</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>43.6772365196078</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>43.0141843971631</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>42.311986863711</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>42.0249418727542</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>41.1410798243795</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>40.9160892994611</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>16206</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Ranquil</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>40.5466970387244</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>16202</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>Cobquecura</t>
         </is>
       </c>
-      <c r="C22">
+      <c r="C33">
+        <v>40.287610619469</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>16206</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Ranquil</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>39.8403448929316</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>39.7552537160431</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>39.4810863239573</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>39.1351805205709</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>16303</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Ñiquén</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>39.0817469204927</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>16303</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Ñiquén</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>38.8257575757576</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>38.7302282243851</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>38.7176220806794</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>38.4372869802318</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>38.015607580825</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>37.2474344658904</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>37.1115483783417</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>36.7311669932506</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>36.4160850154059</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>16303</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Ñiquén</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>36.2559347845561</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>36.0462938913084</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>35.7794663242009</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>35.5472360880015</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>16206</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Ranquil</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>34.1796341796342</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>33.7536873156342</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>33.3565459610028</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>16206</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Ranquil</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>33.2398753894081</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>32.5306730879486</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>32.3821100563402</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>32.2841726618705</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>32.0260149783209</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>31.8803684156059</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>31.7572542052784</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>31.601443948048</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>31.5169769989047</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>31.507024265645</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>31.4467458478177</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>31.3556420513929</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>31.2242074657663</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>30.9509861355204</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C70">
+        <v>30.9331797235023</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>30.840469099032</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C72">
+        <v>30.5208684891439</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C73">
+        <v>30.478195164076</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C74">
+        <v>30.1650615686838</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C75">
+        <v>30.0612020354834</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C76">
+        <v>29.9374137895539</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C77">
+        <v>29.8663820366856</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C78">
+        <v>29.5383743981875</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C79">
+        <v>29.4507426651971</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C80">
+        <v>29.1834002677376</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C81">
+        <v>29.1580489486384</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C82">
+        <v>29.1126543209877</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C83">
+        <v>28.947958725886</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C84">
+        <v>28.6013515771184</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C85">
+        <v>28.0653912848912</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C86">
+        <v>27.673434856176</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C87">
+        <v>27.6000427990584</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C88">
+        <v>27.2144348344766</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C89">
+        <v>27.1908922425205</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C90">
+        <v>26.7626438892971</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>16206</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Ranquil</t>
+        </is>
+      </c>
+      <c r="C91">
+        <v>26.7259259259259</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C92">
+        <v>26.6553287981859</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C93">
+        <v>26.4910536779324</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C94">
+        <v>26.4596015495296</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C95">
+        <v>26.4528756398675</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C96">
+        <v>26.1446551116174</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C97">
+        <v>26.0511486779367</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C98">
+        <v>25.8428627760252</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>16303</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Ñiquén</t>
+        </is>
+      </c>
+      <c r="C99">
+        <v>25.8036677454153</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C100">
+        <v>25.7326085715916</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C101">
+        <v>25.5583909559873</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C102">
+        <v>25.4733432984554</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C103">
+        <v>25.4103129401678</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C104">
+        <v>24.9637624889993</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C105">
+        <v>24.9593179567002</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C106">
+        <v>24.8847926267281</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C107">
+        <v>24.6988740507986</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C108">
+        <v>24.5247160856172</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C109">
+        <v>24.4769706461069</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C110">
+        <v>24.3059233757062</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C111">
+        <v>24.2161716171617</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C112">
+        <v>24.1854457861874</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C113">
+        <v>23.8044158398141</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C114">
+        <v>23.5019727108335</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C115">
+        <v>23.1709333862539</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C116">
+        <v>23.0650372243293</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C117">
+        <v>23.0492741485204</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C118">
         <v>22.6951465775364</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C119">
+        <v>22.6086224317952</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C120">
+        <v>22.3526077097506</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C121">
+        <v>22.3315382491025</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C122">
+        <v>22.3119739342927</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C123">
+        <v>21.6196025698491</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C124">
+        <v>19.9131484835818</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C125">
+        <v>19.8382074194422</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C126">
+        <v>19.5828225416992</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C127">
+        <v>19.1557582969721</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C128">
+        <v>12.0383673903789</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C129">
+        <v>10.9772710977271</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>16303</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Ñiquén</t>
+        </is>
+      </c>
+      <c r="C130">
+        <v>10.9470229723394</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C131">
+        <v>10.3793903247184</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C132">
+        <v>10.1274493357937</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C133">
+        <v>9.83104904749591</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>16206</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Ranquil</t>
+        </is>
+      </c>
+      <c r="C134">
+        <v>9.602302459445321</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C135">
+        <v>9.26236044657097</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C136">
+        <v>9.14116327511617</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C137">
+        <v>8.572507552870089</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C138">
+        <v>8.295707016412241</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C139">
+        <v>8.189975767172919</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C140">
+        <v>7.63095238095238</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C141">
+        <v>7.48567335243553</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C142">
+        <v>7.32775786539227</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C143">
+        <v>7.1027744545092</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C144">
+        <v>7.00915141430948</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C145">
+        <v>6.41044925792218</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C146">
+        <v>5.95097460129947</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C147">
+        <v>5.82087809434844</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C148">
+        <v>5.26008182349503</v>
       </c>
     </row>
   </sheetData>
